--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/pre LAM_HRM-2031-0312/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/pre LAM_HRM-2031-0312/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Back_Summary.xlsx
@@ -434,17 +434,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Bump</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -454,23 +449,25 @@
           <t>Unit 7</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
       <c r="C2" t="n">
-        <v>18.11495</v>
+        <v>17.81018</v>
       </c>
       <c r="D2" t="n">
-        <v>17.51241</v>
+        <v>17.0306</v>
       </c>
       <c r="E2" t="n">
-        <v>17.93143</v>
+        <v>17.12353</v>
       </c>
       <c r="F2" t="n">
-        <v>46.14604</v>
+        <v>22.80579</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05346</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.93819</v>
+        <v>36.76784</v>
       </c>
     </row>
     <row r="3">
@@ -480,22 +477,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.33165</v>
+        <v>18.02408</v>
       </c>
       <c r="D3" t="n">
-        <v>17.64545</v>
+        <v>16.98998</v>
       </c>
       <c r="E3" t="n">
-        <v>17.7949</v>
+        <v>17.47672</v>
       </c>
       <c r="F3" t="n">
-        <v>44.50324</v>
+        <v>22.62913</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05484</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.94058</v>
+        <v>35.9816</v>
       </c>
     </row>
     <row r="4">
@@ -505,22 +499,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.93274</v>
+        <v>17.7262</v>
       </c>
       <c r="D4" t="n">
-        <v>17.82632</v>
+        <v>17.1585</v>
       </c>
       <c r="E4" t="n">
-        <v>17.61862</v>
+        <v>17.67949</v>
       </c>
       <c r="F4" t="n">
-        <v>44.49289</v>
+        <v>22.78309</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05451</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.94906</v>
+        <v>36.88657</v>
       </c>
     </row>
     <row r="5">
@@ -530,22 +521,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.67111</v>
+        <v>17.81528</v>
       </c>
       <c r="D5" t="n">
-        <v>17.55534</v>
+        <v>16.79962</v>
       </c>
       <c r="E5" t="n">
-        <v>17.75628</v>
+        <v>17.6013</v>
       </c>
       <c r="F5" t="n">
-        <v>44.75108</v>
+        <v>22.50605</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05416</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.90897</v>
+        <v>35.48877</v>
       </c>
     </row>
     <row r="6">
@@ -555,22 +543,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.58938</v>
+        <v>17.42551</v>
       </c>
       <c r="D6" t="n">
-        <v>17.29983</v>
+        <v>17.23013</v>
       </c>
       <c r="E6" t="n">
-        <v>17.67236</v>
+        <v>17.23678</v>
       </c>
       <c r="F6" t="n">
-        <v>45.18301</v>
+        <v>22.95611</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0526</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.92566</v>
+        <v>36.30107</v>
       </c>
     </row>
     <row r="7">
@@ -580,22 +565,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18.10341</v>
+        <v>17.58459</v>
       </c>
       <c r="D7" t="n">
-        <v>17.68755</v>
+        <v>17.09318</v>
       </c>
       <c r="E7" t="n">
-        <v>17.8533</v>
+        <v>17.4169</v>
       </c>
       <c r="F7" t="n">
-        <v>45.08693</v>
+        <v>23.11549</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05457</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.98554</v>
+        <v>37.45202</v>
       </c>
     </row>
     <row r="8">
@@ -605,22 +587,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.76124</v>
+        <v>17.60611</v>
       </c>
       <c r="D8" t="n">
-        <v>17.44534</v>
+        <v>16.81117</v>
       </c>
       <c r="E8" t="n">
-        <v>17.9916</v>
+        <v>17.38287</v>
       </c>
       <c r="F8" t="n">
-        <v>45.18418</v>
+        <v>23.21072</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0547</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.97372</v>
+        <v>36.90559</v>
       </c>
     </row>
     <row r="9">
@@ -630,22 +609,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.6469</v>
+        <v>18.14906</v>
       </c>
       <c r="D9" t="n">
-        <v>17.54943</v>
+        <v>16.73692</v>
       </c>
       <c r="E9" t="n">
-        <v>17.90619</v>
+        <v>17.43643</v>
       </c>
       <c r="F9" t="n">
-        <v>43.46011</v>
+        <v>23.3667</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05326</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.94731</v>
+        <v>37.35239</v>
       </c>
     </row>
     <row r="10">
@@ -655,22 +631,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.7865</v>
+        <v>17.81367</v>
       </c>
       <c r="D10" t="n">
-        <v>17.39434</v>
+        <v>17.08327</v>
       </c>
       <c r="E10" t="n">
-        <v>17.56448</v>
+        <v>17.25616</v>
       </c>
       <c r="F10" t="n">
-        <v>45.45707</v>
+        <v>23.30473</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0532</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.90427</v>
+        <v>36.20575</v>
       </c>
     </row>
     <row r="11">
@@ -717,22 +690,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.60106</v>
+        <v>17.80066</v>
       </c>
       <c r="D12" t="n">
-        <v>17.62315</v>
+        <v>17.23564</v>
       </c>
       <c r="E12" t="n">
-        <v>17.42747</v>
+        <v>17.64609</v>
       </c>
       <c r="F12" t="n">
-        <v>44.88755</v>
+        <v>45.04773</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05308</v>
+        <v>0.05394</v>
       </c>
       <c r="H12" t="n">
-        <v>1.93572</v>
+        <v>1.94759</v>
       </c>
     </row>
     <row r="13">
@@ -742,22 +715,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.83067</v>
+        <v>17.87173</v>
       </c>
       <c r="D13" t="n">
-        <v>17.69974</v>
+        <v>17.50595</v>
       </c>
       <c r="E13" t="n">
-        <v>18.12825</v>
+        <v>17.851</v>
       </c>
       <c r="F13" t="n">
-        <v>45.20546</v>
+        <v>45.26029</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05337</v>
+        <v>0.05353</v>
       </c>
       <c r="H13" t="n">
-        <v>1.94296</v>
+        <v>1.91056</v>
       </c>
     </row>
     <row r="14">
@@ -767,22 +740,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18.09593</v>
+        <v>17.85957</v>
       </c>
       <c r="D14" t="n">
-        <v>17.67496</v>
+        <v>17.12335</v>
       </c>
       <c r="E14" t="n">
-        <v>17.7874</v>
+        <v>17.56344</v>
       </c>
       <c r="F14" t="n">
-        <v>45.19404</v>
+        <v>44.70865</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05415</v>
+        <v>0.05399</v>
       </c>
       <c r="H14" t="n">
-        <v>1.89128</v>
+        <v>1.98119</v>
       </c>
     </row>
     <row r="15">
@@ -792,22 +765,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.38502</v>
+        <v>18.10803</v>
       </c>
       <c r="D15" t="n">
-        <v>17.49178</v>
+        <v>17.50736</v>
       </c>
       <c r="E15" t="n">
-        <v>17.76508</v>
+        <v>17.89019</v>
       </c>
       <c r="F15" t="n">
-        <v>45.48904</v>
+        <v>44.7235</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05458</v>
+        <v>0.05217</v>
       </c>
       <c r="H15" t="n">
-        <v>1.91498</v>
+        <v>1.88564</v>
       </c>
     </row>
     <row r="16">
@@ -817,22 +790,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.51085</v>
+        <v>17.95745</v>
       </c>
       <c r="D16" t="n">
-        <v>17.73054</v>
+        <v>17.60547</v>
       </c>
       <c r="E16" t="n">
-        <v>17.80461</v>
+        <v>17.82949</v>
       </c>
       <c r="F16" t="n">
-        <v>45.15185</v>
+        <v>45.25356</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05332</v>
+        <v>0.05525</v>
       </c>
       <c r="H16" t="n">
-        <v>1.95649</v>
+        <v>1.92411</v>
       </c>
     </row>
     <row r="17">
@@ -842,22 +815,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.64468</v>
+        <v>17.81869</v>
       </c>
       <c r="D17" t="n">
-        <v>17.98771</v>
+        <v>17.28705</v>
       </c>
       <c r="E17" t="n">
-        <v>17.6624</v>
+        <v>17.31281</v>
       </c>
       <c r="F17" t="n">
-        <v>44.68183</v>
+        <v>44.63136</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05345</v>
+        <v>0.05392</v>
       </c>
       <c r="H17" t="n">
-        <v>1.87709</v>
+        <v>1.90608</v>
       </c>
     </row>
     <row r="18">
@@ -867,22 +840,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.66679</v>
+        <v>17.705</v>
       </c>
       <c r="D18" t="n">
-        <v>17.41278</v>
+        <v>17.46905</v>
       </c>
       <c r="E18" t="n">
-        <v>17.50888</v>
+        <v>17.61224</v>
       </c>
       <c r="F18" t="n">
-        <v>44.71216</v>
+        <v>44.89091</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05311</v>
+        <v>0.05332</v>
       </c>
       <c r="H18" t="n">
-        <v>1.95481</v>
+        <v>1.94608</v>
       </c>
     </row>
     <row r="19">
@@ -892,22 +865,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.81657</v>
+        <v>17.93949</v>
       </c>
       <c r="D19" t="n">
-        <v>17.33482</v>
+        <v>17.63264</v>
       </c>
       <c r="E19" t="n">
-        <v>17.8673</v>
+        <v>17.68792</v>
       </c>
       <c r="F19" t="n">
-        <v>45.01689</v>
+        <v>44.04919</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05416</v>
+        <v>0.05242</v>
       </c>
       <c r="H19" t="n">
-        <v>1.91142</v>
+        <v>1.90093</v>
       </c>
     </row>
     <row r="20">
@@ -917,22 +890,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.28736</v>
+        <v>17.98123</v>
       </c>
       <c r="D20" t="n">
-        <v>17.35139</v>
+        <v>17.63204</v>
       </c>
       <c r="E20" t="n">
-        <v>17.40555</v>
+        <v>17.68712</v>
       </c>
       <c r="F20" t="n">
-        <v>45.14828</v>
+        <v>46.02094</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05289</v>
+        <v>0.05392</v>
       </c>
       <c r="H20" t="n">
-        <v>1.94402</v>
+        <v>1.94666</v>
       </c>
     </row>
   </sheetData>
